--- a/results/Supplementary_Tables_S1-S4.xlsx
+++ b/results/Supplementary_Tables_S1-S4.xlsx
@@ -35,7 +35,7 @@
     <t xml:space="preserve">S1_ConfigA — BenchmarkDotNet statistics of configuration A (laptop Acer Nitro V 15; Intel Core i5-13420H, 16 GB DDR5-5200, Intel UHD Graphics via OpenCL, NVIDIA GeForce RTX 4050 Laptop GPU via CUDA; Windows 11 25H2; .NET 7.0.16; BenchmarkDotNet 0.15.8), both chunk-size series (512 KB and 1024 KB). Times in milliseconds. CI = half-width of the 99.9% confidence interval of the mean as reported by BenchmarkDotNet ("Error" column). Alloc = managed memory allocated per operation; Gen0/1/2 = collections per 1000 operations.</t>
   </si>
   <si>
-    <t xml:space="preserve">   Source: BenchmarkDotNet summary reports of the original measurement campaign (thesis, Appendix 4; reproduced in the repository given in the Data Availability Statement). Values were transcribed from the reports and checked against them. N, which the reports do not print, is (SD/SE)^2, in agreement with the reported CI. The 1024 KB series is confounded at volumes of 3.45 MB and above (Section 7.8 of the manuscript).</t>
+    <t xml:space="preserve">   Source: BenchmarkDotNet summary reports of the original measurement campaign (thesis, Appendix 4; reproduced in results/configuration_A/reports of the repository https://github.com/CSharpCooking/AssociativeProtectionGPU). Values were transcribed from the reports and checked against them. N, which the reports do not print, is (SD/SE)^2, in agreement with the reported CI. The 1024 KB series is confounded at volumes of 3.45 MB and above (Section 7.8 of the manuscript).</t>
   </si>
   <si>
     <t xml:space="preserve">S2_ConfigBC — measurements of configurations B (virtual machine, 2 vCPUs of an Intel Xeon processor, Ubuntu 24.04.5, .NET 8.0.32, OpenSSL) and C (laptop HP OMEN 15-dc1xxx, Intel Core i5-9300H, 4 cores / 8 threads, 16 GB, Windows 11 build 26300, .NET 8.0.33, BCryptGenRandom, High performance power plan): formation variants (10 MB English text) and recognition variants (six 10 MB inputs); 2 warm-up and 10 measured iterations, new key in every iteration; times in ms, raw iterations included. "all threads" = 2 threads on B and 8 threads on C.</t>
